--- a/02_Zero_Shot/outputs/NLI/roberta-large-mnli/RESULT_clap_roberta-large-mnli_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/NLI/roberta-large-mnli/RESULT_clap_roberta-large-mnli_zeroshot.xlsx
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>228.4333417550006</v>
+        <v>312.0554511949995</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07614444725166686</v>
+        <v>0.1040184837316665</v>
       </c>
     </row>
   </sheetData>
